--- a/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99A61A93-BD38-4AEA-AE23-1F16DD89BDBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F285DAAF-E6E4-4DF4-AE76-7D1EF491D40F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C29B28A-3EC2-4DC4-866E-F15A900E2A78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8904912F-5667-4ACB-BD3E-B635521CC3A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B53DBB5-020D-4FC4-9295-2D3F57F5EC36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1F8977-2E56-4B00-9E12-CFB8F2DF60A0}"/>
 </file>